--- a/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
+++ b/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rbd488bd3a3244fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8e166a62c9ee48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R68e24ef64bcf402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rfdaa6cb1c7d0499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rdb83fb37c11a49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R10bc3ca2450d4d8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -662,16 +662,16 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="23" t="str">
-        <x:v>text</x:v>
+        <x:v>select_one kpi_ids</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
         <x:v>id_kpi</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>ID KPI</x:v>
+        <x:v>ID KPI officiel</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Meme ID KPI que dans le formulaire 1.</x:v>
+        <x:v>Choisir le meme ID KPI que dans le Formulaire 1. Ne pas saisir un KPI qui n'existe pas au referentiel.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
         <x:v>yes</x:v>
@@ -680,7 +680,9 @@
       <x:c r="G7" s="24" t="str"/>
       <x:c r="H7" s="24" t="str"/>
       <x:c r="I7" s="24" t="str"/>
-      <x:c r="J7" s="25" t="str"/>
+      <x:c r="J7" s="25" t="str">
+        <x:v>autocomplete</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -1390,6 +1392,820 @@
       </x:c>
       <x:c r="C44" s="28" t="str">
         <x:v>Rejete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>KPI-001</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>KPI-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>KPI-002</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>KPI-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>KPI-003</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>KPI-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>KPI-004</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>KPI-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>KPI-005</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>KPI-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>KPI-006</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>KPI-006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>KPI-007</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>KPI-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>KPI-008</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>KPI-008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>KPI-009</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>KPI-009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>KPI-010</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>KPI-010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>KPI-011</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>KPI-011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>KPI-012</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>KPI-012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>KPI-013</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>KPI-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>KPI-014</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>KPI-014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>KPI-015</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>KPI-015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>KPI-016</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>KPI-016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>KPI-017</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>KPI-017</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>KPI-018</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>KPI-018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>KPI-019</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>KPI-019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>KPI-020</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>KPI-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>KPI-021</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>KPI-021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>KPI-022</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>KPI-022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>KPI-023</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>KPI-023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>KPI-024</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>KPI-024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>KPI-025</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>KPI-025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>KPI-026</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>KPI-026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>KPI-027</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>KPI-027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>KPI-028</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>KPI-028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>KPI-029</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>KPI-029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>KPI-030</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>KPI-030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>KPI-031</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>KPI-031</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>KPI-032</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>KPI-032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>KPI-033</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>KPI-033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>KPI-034</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>KPI-034</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>KPI-035</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>KPI-035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>KPI-036</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>KPI-036</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>KPI-037</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>KPI-037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>KPI-038</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>KPI-038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>KPI-039</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>KPI-039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>KPI-040</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>KPI-040</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>KPI-041</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>KPI-041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>KPI-042</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>KPI-042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>KPI-043</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>KPI-043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>KPI-044</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>KPI-044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>KPI-045</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>KPI-045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>KPI-046</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>KPI-046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>KPI-047</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>KPI-047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>KPI-048</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>KPI-048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>KPI-049</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>KPI-049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>KPI-050</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>KPI-050</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>KPI-051</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>KPI-051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>KPI-052</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>KPI-052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>KPI-053</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>KPI-053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>KPI-054</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>KPI-054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>KPI-055</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>KPI-055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>KPI-056</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>KPI-056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>KPI-057</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>KPI-057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>KPI-058</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>KPI-058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>KPI-059</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>KPI-059</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>KPI-060</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>KPI-060</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>KPI-061</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>KPI-061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>KPI-062</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>KPI-062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>KPI-063</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>KPI-063</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>KPI-064</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>KPI-064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>KPI-065</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>KPI-065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>KPI-066</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>KPI-066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>KPI-067</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>KPI-067</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>KPI-068</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>KPI-068</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>KPI-069</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>KPI-069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>KPI-070</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>KPI-070</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>KPI-071</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>KPI-071</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>KPI-072</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>KPI-072</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>KPI-073</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>KPI-073</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>KPI-074</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>KPI-074</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
+++ b/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rfdaa6cb1c7d0499f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rdb83fb37c11a49c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R10bc3ca2450d4d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra918cb39d2964a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rd2c57d59ce02402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R4c95289b952246ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -671,7 +671,7 @@
         <x:v>ID KPI officiel</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Choisir le meme ID KPI que dans le Formulaire 1. Ne pas saisir un KPI qui n'existe pas au referentiel.</x:v>
+        <x:v>Choisir le meme ID KPI que dans le Formulaire 1. La valeur sauvegardee reste l'ID KPI seul.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
         <x:v>yes</x:v>
@@ -1402,7 +1402,7 @@
         <x:v>KPI-001</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>KPI-001</x:v>
+        <x:v>KPI-001 - Chiffre d'affaires | Calcul: Volume produit x Prix unitaire HT | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1413,7 +1413,7 @@
         <x:v>KPI-002</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>KPI-002</x:v>
+        <x:v>KPI-002 - Taux de maintenance préventive réalisés | Calcul: Nbre de maintenance préventive réalisé X 100) / Nbr de maintenance préve... | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1424,7 +1424,7 @@
         <x:v>KPI-003</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>KPI-003</x:v>
+        <x:v>KPI-003 - Disponibilité / Accessibilité (système) | Calcul: Nombre de minutes de disponibilité des systèmes d’information X100) / To... | Cible: 98</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1435,7 +1435,7 @@
         <x:v>KPI-004</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>KPI-004</x:v>
+        <x:v>KPI-004 - Transactions Bloquées (télécommunication) | Calcul: Nombre d’appels aboutissant à une tonalité d’occupation X100) / nombre t... | Cible: 98</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1446,7 +1446,7 @@
         <x:v>KPI-005</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>KPI-005</x:v>
+        <x:v>KPI-005 - Taux de Disponibilité / Accessibilité (télécommunica... | Calcul: Nombre de minutes de disponibilité du commutateur X100) / Total des minu... | Cible: 98</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1457,7 +1457,7 @@
         <x:v>KPI-006</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>KPI-006</x:v>
+        <x:v>KPI-006 - VOLUME IVR | Calcul: Nombre total de transaction éligible pour le service | Cible: 98</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1468,7 +1468,7 @@
         <x:v>KPI-007</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>KPI-007</x:v>
+        <x:v>KPI-007 - TAUX DE FONCTIONNALITE DES SYSTEMES IVR | Calcul: Somme des temps d'indisponibilité X 100) / Temps total de disponibilité | Cible: 99</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1479,7 +1479,7 @@
         <x:v>KPI-008</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>KPI-008</x:v>
+        <x:v>KPI-008 - Nombre d'incident de sécurité | Calcul: Nombre total d'incidents identifié sur le système informatique | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1490,7 +1490,7 @@
         <x:v>KPI-009</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>KPI-009</x:v>
+        <x:v>KPI-009 - Taux de traitement dans les délais | Calcul: Nbre de ticket ouvert traités dans le délais(2880min)X100 / Nbre total d... | Cible: 89</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1501,7 +1501,7 @@
         <x:v>KPI-010</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>KPI-010</x:v>
+        <x:v>KPI-010 - MTTR | Calcul: Moyenne de temps de traitement de tous les tickets sur la periode | Cible: 60</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1512,7 +1512,7 @@
         <x:v>KPI-011</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>KPI-011</x:v>
+        <x:v>KPI-011 - Taux d'exactitude de réparation ou solution | Calcul: Volume total de tickets ouverts - Volume de tickets réouverts)X 100 / no... | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1523,7 +1523,7 @@
         <x:v>KPI-012</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>KPI-012</x:v>
+        <x:v>KPI-012 - Tx Exact ECC | Calcul: Tx Exact ECC=Nb transactions sans ECC X 100/Nb transactions évaluées | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -1534,7 +1534,7 @@
         <x:v>KPI-013</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>KPI-013</x:v>
+        <x:v>KPI-013 - Tx Exact ECA | Calcul: Tx Exact ECA=Nb transactions sans ECA X 100/Nb transactions évaluées | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1545,7 +1545,7 @@
         <x:v>KPI-014</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>KPI-014</x:v>
+        <x:v>KPI-014 - Tx Exact ECCo | Calcul: Tx Exact ECCo=Nb transactions sans ECCo X 100/Nb transactions évaluées | Cible: 99.5</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1556,7 +1556,7 @@
         <x:v>KPI-015</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>KPI-015</x:v>
+        <x:v>KPI-015 - Tx Exact ENC | Calcul: Tx Exact ENC=Nb transactions sans ENC X 100/Nb transactions évaluées | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1567,7 +1567,7 @@
         <x:v>KPI-016</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>KPI-016</x:v>
+        <x:v>KPI-016 - Tx défaut | Calcul: Tx défaut=Nb d'inconformité X 100/Nb transactions évaluées | Cible: 2</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -1578,7 +1578,7 @@
         <x:v>KPI-017</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>KPI-017</x:v>
+        <x:v>KPI-017 - Tx per de Esc | Calcul: Tx per de Esc= Pertinence de l’escalade = Nb d’escalades incorrectes / N... | Cible: 98</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1589,7 +1589,7 @@
         <x:v>KPI-018</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>KPI-018</x:v>
+        <x:v>KPI-018 - VR | Calcul: VR=Echantillonnage représentatif sur le volume d’appels reçu. Calcul eff... | Cible: 600</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1600,7 +1600,7 @@
         <x:v>KPI-019</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>KPI-019</x:v>
+        <x:v>KPI-019 - Taux de réussite Quiz FI | Calcul: Nombre d'apprenants ayant validé le quiz ÷ Nombre total d'apprenants aya... | Cible: 85</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1611,7 +1611,7 @@
         <x:v>KPI-020</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>KPI-020</x:v>
+        <x:v>KPI-020 - Heures FI (Prévues vs Réalisées) | Calcul: Heures FI réalisées /Heures FI prévues)​ * 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1622,7 +1622,7 @@
         <x:v>KPI-021</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>KPI-021</x:v>
+        <x:v>KPI-021 - Taux Présence Ateliers | Calcul: Nombre d'agents présents aux ateliers de formation ÷ Nombre d'agents con... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1633,7 +1633,7 @@
         <x:v>KPI-022</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>KPI-022</x:v>
+        <x:v>KPI-022 - Taux de Présence au Coaching | Calcul: Nombre de séances de coaching réalisées ÷ Nombre de séances de coaching ... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -1644,7 +1644,7 @@
         <x:v>KPI-023</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>KPI-023</x:v>
+        <x:v>KPI-023 - Heures FC (Prévues vs Réalisées) | Calcul: Heures FC réalisées ÷ Heures FC prévues) × 100 | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -1655,7 +1655,7 @@
         <x:v>KPI-024</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>KPI-024</x:v>
+        <x:v>KPI-024 - Taux de Réussite Quiz FC | Calcul: Nombre d'agents ayant atteint ou dépassé le score minimum requis ÷ Nombr... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1666,7 +1666,7 @@
         <x:v>KPI-025</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>KPI-025</x:v>
+        <x:v>KPI-025 - Score Quiz FC | Calcul: Somme des scores individuels obtenus aux quiz FC ÷ Nombre total d'agents... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -1677,7 +1677,7 @@
         <x:v>KPI-026</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>KPI-026</x:v>
+        <x:v>KPI-026 - Taux de complétion EDFLEX | Calcul: Nombre de parcours complétés ÷ Nombre de parcours assignés) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -1688,7 +1688,7 @@
         <x:v>KPI-027</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>KPI-027</x:v>
+        <x:v>KPI-027 - Qualité de la Formation CRCD — Intégration | Calcul: Nombre d'agents ayant réussi au quiz ÷ Nombre total d'agents évalués) × 100 | Cible: 85</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -1699,7 +1699,7 @@
         <x:v>KPI-028</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>KPI-028</x:v>
+        <x:v>KPI-028 - Qualité de la Formation CRCD — Continue | Calcul: Nombre d'agents ayant atteint le seuil ÷ Nombre total d'agents évalués) ... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -1710,7 +1710,7 @@
         <x:v>KPI-029</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>KPI-029</x:v>
+        <x:v>KPI-029 - Efficacité de la Formation | Calcul: Une enquête de satisfaction sur le déroulé de la formation | Cible: 80</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -1721,7 +1721,7 @@
         <x:v>KPI-030</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>KPI-030</x:v>
+        <x:v>KPI-030 - Efficacité du Formateur | Calcul: feedbacks à chaud ( enquête de satisfaction) | Cible: 80</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -1732,7 +1732,7 @@
         <x:v>KPI-031</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>KPI-031</x:v>
+        <x:v>KPI-031 - Taux de Formation Réalisée | Calcul: Nombre de formation réalisée / Nombre de formation prévue) * 100 | Cible: 60</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -1743,7 +1743,7 @@
         <x:v>KPI-032</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>KPI-032</x:v>
+        <x:v>KPI-032 - FOLLOWERS LINKEDIN | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -1754,7 +1754,7 @@
         <x:v>KPI-033</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>KPI-033</x:v>
+        <x:v>KPI-033 - FOLLOWERS FACEBOOK | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -1765,7 +1765,7 @@
         <x:v>KPI-034</x:v>
       </x:c>
       <x:c r="C78" t="str">
-        <x:v>KPI-034</x:v>
+        <x:v>KPI-034 - FOLLOWERS INSTAGRAM | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -1776,7 +1776,7 @@
         <x:v>KPI-035</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>KPI-035</x:v>
+        <x:v>KPI-035 - FOLLOWERS SUR X (Twitter) | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -1787,7 +1787,7 @@
         <x:v>KPI-036</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>KPI-036</x:v>
+        <x:v>KPI-036 - IMPRESSION (LINKEDIN) | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -1798,7 +1798,7 @@
         <x:v>KPI-037</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>KPI-037</x:v>
+        <x:v>KPI-037 - PORTEE (FACEBOOK) | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -1809,7 +1809,7 @@
         <x:v>KPI-038</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>KPI-038</x:v>
+        <x:v>KPI-038 - PORTEE (INSTAGRAM) | Calcul: NA | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -1820,7 +1820,7 @@
         <x:v>KPI-039</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>KPI-039</x:v>
+        <x:v>KPI-039 - TAUX D'ENGAGEMENT | Calcul: INTERACTIONS/IMPRESSIONS) *100 | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -1831,7 +1831,7 @@
         <x:v>KPI-040</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>KPI-040</x:v>
+        <x:v>KPI-040 - TAUX D'ENGAGEMENT FACEBOOK | Calcul: INTERACTIONS/PORTEE) * 100 | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -1842,7 +1842,7 @@
         <x:v>KPI-041</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>KPI-041</x:v>
+        <x:v>KPI-041 - TAUX D'ENGAGEMENT INSTAGRAM | Calcul: INTERACTIONS/PORTEE) *100 | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -1853,7 +1853,7 @@
         <x:v>KPI-042</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>KPI-042</x:v>
+        <x:v>KPI-042 - Masse Salariale | Calcul: Total des charges RH sur le total du Chiffre d'affaires | Cible: 35</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -1864,7 +1864,7 @@
         <x:v>KPI-043</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>KPI-043</x:v>
+        <x:v>KPI-043 - Résultat Avant Impôt | Calcul: Chiffre d'affaires - toutes charges) / Chiffre d'affaires | Cible: 15</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -1875,7 +1875,7 @@
         <x:v>KPI-044</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>KPI-044</x:v>
+        <x:v>KPI-044 - Taux de transformation digital | Calcul: Somme (%projet) / Nombre de projets | Cible: 70</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -1886,7 +1886,7 @@
         <x:v>KPI-045</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>KPI-045</x:v>
+        <x:v>KPI-045 - Taux de recouvrement | Calcul: Somme des encaissements sur la période / Somme des créances exigibles su... | Cible: 75</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -1897,7 +1897,7 @@
         <x:v>KPI-046</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>KPI-046</x:v>
+        <x:v>KPI-046 - Créances clients | Calcul: Somme des factures émises échues sur une période donnée | Cible: 1</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -1908,7 +1908,7 @@
         <x:v>KPI-047</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>KPI-047</x:v>
+        <x:v>KPI-047 - Encours Clients | Calcul: Somme des créances clients (Factures échues et non échues) + Commandes e... | Cible: 1</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -1919,7 +1919,7 @@
         <x:v>KPI-048</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>KPI-048</x:v>
+        <x:v>KPI-048 - Balance Âgée | Calcul: Date du jour - date d'échéance de la facture | Cible: 25</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -1930,7 +1930,7 @@
         <x:v>KPI-049</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>KPI-049</x:v>
+        <x:v>KPI-049 - DSO (Days Sales Outstanding) | Calcul: Créances clients / Chiffre d’affaires TTC sur la période) × Nombre de jo... | Cible: 45</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -1941,7 +1941,7 @@
         <x:v>KPI-050</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>KPI-050</x:v>
+        <x:v>KPI-050 - Point des Encaissements | Calcul: Somme réelle des encaissements sur une période donnée (virements, chèque... | Cible: 1</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -1952,7 +1952,7 @@
         <x:v>KPI-051</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>KPI-051</x:v>
+        <x:v>KPI-051 - Créances Irrécouvrables | Calcul: Créances douteuses / CA total). | Cible: 5</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -1963,7 +1963,7 @@
         <x:v>KPI-052</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>KPI-052</x:v>
+        <x:v>KPI-052 - ADHERENCE HEURE | Calcul: Heures réalisées (temps total de présence - temps de déjeuner) /heures p... | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -1974,7 +1974,7 @@
         <x:v>KPI-053</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>KPI-053</x:v>
+        <x:v>KPI-053 - TAUX D'OCCUPATION | Calcul: Traitement + attente ) /( Traitement + attente + post appel ) )* 100 | Cible: 75</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -1985,7 +1985,7 @@
         <x:v>KPI-054</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>KPI-054</x:v>
+        <x:v>KPI-054 - ADHERENCE PLANNING | Calcul: ETP (EFFECTIF TOTAL PLANIFIES) / BESOIN ) )* 100 | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -1996,7 +1996,7 @@
         <x:v>KPI-055</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>KPI-055</x:v>
+        <x:v>KPI-055 - QUALITE DE PREVISION | Calcul: RECUS / PREVUS | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -2007,7 +2007,7 @@
         <x:v>KPI-056</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>KPI-056</x:v>
+        <x:v>KPI-056 - EFFICACITE | Calcul: TRAITES/RECUS | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -2018,7 +2018,7 @@
         <x:v>KPI-057</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>KPI-057</x:v>
+        <x:v>KPI-057 - Volume total des achats | Calcul: Somme des montants des bons de commande et bons d'achat émis sur la période | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2029,7 +2029,7 @@
         <x:v>KPI-058</x:v>
       </x:c>
       <x:c r="C102" t="str">
-        <x:v>KPI-058</x:v>
+        <x:v>KPI-058 - Taux de conformité des bons de commande | Calcul: Nombre de bons de commande conformes / Nombre total de bons de commande)... | Cible: 95</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2040,7 +2040,7 @@
         <x:v>KPI-059</x:v>
       </x:c>
       <x:c r="C103" t="str">
-        <x:v>KPI-059</x:v>
+        <x:v>KPI-059 - Taux de non-conformité des produits | Calcul: Nombre de produits retournés ou non conformes / Total des produits achet... | Cible: 1</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2051,7 +2051,7 @@
         <x:v>KPI-060</x:v>
       </x:c>
       <x:c r="C104" t="str">
-        <x:v>KPI-060</x:v>
+        <x:v>KPI-060 - Délai moyen d'approvisionnement | Calcul: Somme des délais individuels d'approvisionnement / Nombre de demandes tr... | Cible: a definir</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2062,7 +2062,7 @@
         <x:v>KPI-061</x:v>
       </x:c>
       <x:c r="C105" t="str">
-        <x:v>KPI-061</x:v>
+        <x:v>KPI-061 - Taux de service client | Calcul: Nombre de demandes satisfaites / Nombre total de demandes exprimées) × 100 | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -2073,7 +2073,7 @@
         <x:v>KPI-062</x:v>
       </x:c>
       <x:c r="C106" t="str">
-        <x:v>KPI-062</x:v>
+        <x:v>KPI-062 - Taux de disponibilité du stock critique | Calcul: Nombre d'articles critiques disponibles / Nombre total d'articles critiq... | Cible: 90</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -2084,7 +2084,7 @@
         <x:v>KPI-063</x:v>
       </x:c>
       <x:c r="C107" t="str">
-        <x:v>KPI-063</x:v>
+        <x:v>KPI-063 - OOS | Calcul: TRO OOS (%) = Objectif (%) /Réalisé(%) | Cible: 19.7</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -2095,7 +2095,7 @@
         <x:v>KPI-064</x:v>
       </x:c>
       <x:c r="C108" t="str">
-        <x:v>KPI-064</x:v>
+        <x:v>KPI-064 - DTR (Direct To Retail) | Calcul: TRO DTR (%) = (Réalisé DTR / Objectif DTR) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -2106,7 +2106,7 @@
         <x:v>KPI-065</x:v>
       </x:c>
       <x:c r="C109" t="str">
-        <x:v>KPI-065</x:v>
+        <x:v>KPI-065 - DTC (Direct To Consumer) | Calcul: TRO DTC (%) = (Réalisé DTC / Objectif DTC) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2117,7 +2117,7 @@
         <x:v>KPI-066</x:v>
       </x:c>
       <x:c r="C110" t="str">
-        <x:v>KPI-066</x:v>
+        <x:v>KPI-066 - ADU (Active Data Users) | Calcul: TRO ADU (%) = (ADU Réalisé / ADU Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2128,7 +2128,7 @@
         <x:v>KPI-067</x:v>
       </x:c>
       <x:c r="C111" t="str">
-        <x:v>KPI-067</x:v>
+        <x:v>KPI-067 - MAU (MoMo Active Users) | Calcul: TRO MAU (%) = (MAU Réalisé / MAU Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2139,7 +2139,7 @@
         <x:v>KPI-068</x:v>
       </x:c>
       <x:c r="C112" t="str">
-        <x:v>KPI-068</x:v>
+        <x:v>KPI-068 - FTTH (Fiber To The Home) | Calcul: TRO FTTH (%) = (FTTH Réalisé / FTTH Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2150,7 +2150,7 @@
         <x:v>KPI-069</x:v>
       </x:c>
       <x:c r="C113" t="str">
-        <x:v>KPI-069</x:v>
+        <x:v>KPI-069 - FWA (Fixed Wireless Access) | Calcul: TRO FWA (%) = (FWA Réalisé / FWA Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2161,7 +2161,7 @@
         <x:v>KPI-070</x:v>
       </x:c>
       <x:c r="C114" t="str">
-        <x:v>KPI-070</x:v>
+        <x:v>KPI-070 - Services at Touch Point (SATP) | Calcul: SATP(%) = (NPS AGENT + NPS AGENCE)/2 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2172,7 +2172,7 @@
         <x:v>KPI-071</x:v>
       </x:c>
       <x:c r="C115" t="str">
-        <x:v>KPI-071</x:v>
+        <x:v>KPI-071 - Recrutement Commerciaux (MRE) | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2183,7 +2183,7 @@
         <x:v>KPI-072</x:v>
       </x:c>
       <x:c r="C116" t="str">
-        <x:v>KPI-072</x:v>
+        <x:v>KPI-072 - Performance MRE | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2194,7 +2194,7 @@
         <x:v>KPI-073</x:v>
       </x:c>
       <x:c r="C117" t="str">
-        <x:v>KPI-073</x:v>
+        <x:v>KPI-073 - Recrutement TDR | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2205,7 +2205,1393 @@
         <x:v>KPI-074</x:v>
       </x:c>
       <x:c r="C118" t="str">
-        <x:v>KPI-074</x:v>
+        <x:v>KPI-074 - Performance TDR | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>KPI-075</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>KPI-075 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>KPI-076</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>KPI-076 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>KPI-077</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>KPI-077 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>KPI-078</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>KPI-078 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>KPI-079</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>KPI-079 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>KPI-080</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>KPI-080 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>KPI-081</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>KPI-081 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>KPI-082</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>KPI-082 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>KPI-083</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>KPI-083 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>KPI-084</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>KPI-084 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>KPI-085</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>KPI-085 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>KPI-086</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>KPI-086 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>KPI-087</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>KPI-087 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>KPI-088</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>KPI-088 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>KPI-089</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>KPI-089 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>KPI-090</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>KPI-090 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>KPI-091</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>KPI-091 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>KPI-092</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>KPI-092 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>KPI-093</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>KPI-093 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>KPI-094</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>KPI-094 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>KPI-095</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>KPI-095 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>KPI-096</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>KPI-096 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>KPI-097</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>KPI-097 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>KPI-098</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>KPI-098 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>KPI-099</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>KPI-099 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>KPI-100</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>KPI-100 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>KPI-101</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>KPI-101 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>KPI-102</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>KPI-102 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>KPI-103</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>KPI-103 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>KPI-104</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>KPI-104 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>KPI-105</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>KPI-105 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>KPI-106</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>KPI-106 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>KPI-107</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>KPI-107 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>KPI-108</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>KPI-108 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>KPI-109</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>KPI-109 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>KPI-110</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>KPI-110 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>KPI-111</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>KPI-111 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>KPI-112</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>KPI-112 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>KPI-113</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>KPI-113 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>KPI-114</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>KPI-114 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>KPI-115</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>KPI-115 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>KPI-116</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>KPI-116 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>KPI-117</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>KPI-117 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>KPI-118</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>KPI-118 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>KPI-119</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>KPI-119 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>KPI-120</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>KPI-120 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>KPI-121</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>KPI-121 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B166" t="str">
+        <x:v>KPI-122</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>KPI-122 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B167" t="str">
+        <x:v>KPI-123</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>KPI-123 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B168" t="str">
+        <x:v>KPI-124</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>KPI-124 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B169" t="str">
+        <x:v>KPI-125</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>KPI-125 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>KPI-126</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>KPI-126 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>KPI-127</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>KPI-127 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>KPI-128</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>KPI-128 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>KPI-129</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>KPI-129 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>KPI-130</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>KPI-130 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>KPI-131</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>KPI-131 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>KPI-132</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>KPI-132 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>KPI-133</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>KPI-133 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>KPI-134</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>KPI-134 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>KPI-135</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>KPI-135 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B180" t="str">
+        <x:v>KPI-136</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>KPI-136 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
+        <x:v>KPI-137</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>KPI-137 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>KPI-138</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>KPI-138 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>KPI-139</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>KPI-139 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>KPI-140</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>KPI-140 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B185" t="str">
+        <x:v>KPI-141</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>KPI-141 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B186" t="str">
+        <x:v>KPI-142</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>KPI-142 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>KPI-143</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>KPI-143 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>KPI-144</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>KPI-144 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B189" t="str">
+        <x:v>KPI-145</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>KPI-145 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B190" t="str">
+        <x:v>KPI-146</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>KPI-146 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B191" t="str">
+        <x:v>KPI-147</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>KPI-147 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B192" t="str">
+        <x:v>KPI-148</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>KPI-148 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>KPI-149</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>KPI-149 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>KPI-150</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>KPI-150 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>KPI-151</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>KPI-151 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>KPI-152</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>KPI-152 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>KPI-153</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>KPI-153 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>KPI-154</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>KPI-154 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>KPI-155</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>KPI-155 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>KPI-156</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>KPI-156 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>KPI-157</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>KPI-157 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>KPI-158</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>KPI-158 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B203" t="str">
+        <x:v>KPI-159</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>KPI-159 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B204" t="str">
+        <x:v>KPI-160</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>KPI-160 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B205" t="str">
+        <x:v>KPI-161</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>KPI-161 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B206" t="str">
+        <x:v>KPI-162</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>KPI-162 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B207" t="str">
+        <x:v>KPI-163</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>KPI-163 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B208" t="str">
+        <x:v>KPI-164</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>KPI-164 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>KPI-165</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>KPI-165 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>KPI-166</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>KPI-166 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>KPI-167</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>KPI-167 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B212" t="str">
+        <x:v>KPI-168</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>KPI-168 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B213" t="str">
+        <x:v>KPI-169</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>KPI-169 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B214" t="str">
+        <x:v>KPI-170</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>KPI-170 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B215" t="str">
+        <x:v>KPI-171</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>KPI-171 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B216" t="str">
+        <x:v>KPI-172</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>KPI-172 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B217" t="str">
+        <x:v>KPI-173</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>KPI-173 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B218" t="str">
+        <x:v>KPI-174</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>KPI-174 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B219" t="str">
+        <x:v>KPI-175</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>KPI-175 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B220" t="str">
+        <x:v>KPI-176</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>KPI-176 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B221" t="str">
+        <x:v>KPI-177</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>KPI-177 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B222" t="str">
+        <x:v>KPI-178</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>KPI-178 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B223" t="str">
+        <x:v>KPI-179</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>KPI-179 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B224" t="str">
+        <x:v>KPI-180</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>KPI-180 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B225" t="str">
+        <x:v>KPI-181</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>KPI-181 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B226" t="str">
+        <x:v>KPI-182</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>KPI-182 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>KPI-183</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>KPI-183 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B228" t="str">
+        <x:v>KPI-184</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>KPI-184 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B229" t="str">
+        <x:v>KPI-185</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>KPI-185 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B230" t="str">
+        <x:v>KPI-186</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>KPI-186 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B231" t="str">
+        <x:v>KPI-187</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>KPI-187 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B232" t="str">
+        <x:v>KPI-188</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>KPI-188 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B233" t="str">
+        <x:v>KPI-189</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>KPI-189 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B234" t="str">
+        <x:v>KPI-190</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>KPI-190 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B235" t="str">
+        <x:v>KPI-191</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>KPI-191 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B236" t="str">
+        <x:v>KPI-192</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>KPI-192 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B237" t="str">
+        <x:v>KPI-193</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>KPI-193 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B238" t="str">
+        <x:v>KPI-194</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>KPI-194 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B239" t="str">
+        <x:v>KPI-195</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>KPI-195 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B240" t="str">
+        <x:v>KPI-196</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>KPI-196 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B241" t="str">
+        <x:v>KPI-197</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>KPI-197 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B242" t="str">
+        <x:v>KPI-198</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>KPI-198 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B243" t="str">
+        <x:v>KPI-199</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>KPI-199 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="str">
+        <x:v>kpi_ids</x:v>
+      </x:c>
+      <x:c r="B244" t="str">
+        <x:v>KPI-200</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>KPI-200 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
+++ b/kobo_forms/PMS_GMC_Formulaire_Objectifs_Mensuels_2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra918cb39d2964a69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rd2c57d59ce02402a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R4c95289b952246ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra047bca16c2042f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R022c4387a9534d1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rebb0059311b6413f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1399,7 +1399,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>KPI-001</x:v>
+        <x:v>KPI_001</x:v>
       </x:c>
       <x:c r="C45" t="str">
         <x:v>KPI-001 - Chiffre d'affaires | Calcul: Volume produit x Prix unitaire HT | Cible: 100</x:v>
@@ -1410,7 +1410,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>KPI-002</x:v>
+        <x:v>KPI_002</x:v>
       </x:c>
       <x:c r="C46" t="str">
         <x:v>KPI-002 - Taux de maintenance préventive réalisés | Calcul: Nbre de maintenance préventive réalisé X 100) / Nbr de maintenance préve... | Cible: 90</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>KPI-003</x:v>
+        <x:v>KPI_003</x:v>
       </x:c>
       <x:c r="C47" t="str">
         <x:v>KPI-003 - Disponibilité / Accessibilité (système) | Calcul: Nombre de minutes de disponibilité des systèmes d’information X100) / To... | Cible: 98</x:v>
@@ -1432,7 +1432,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>KPI-004</x:v>
+        <x:v>KPI_004</x:v>
       </x:c>
       <x:c r="C48" t="str">
         <x:v>KPI-004 - Transactions Bloquées (télécommunication) | Calcul: Nombre d’appels aboutissant à une tonalité d’occupation X100) / nombre t... | Cible: 98</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>KPI-005</x:v>
+        <x:v>KPI_005</x:v>
       </x:c>
       <x:c r="C49" t="str">
         <x:v>KPI-005 - Taux de Disponibilité / Accessibilité (télécommunica... | Calcul: Nombre de minutes de disponibilité du commutateur X100) / Total des minu... | Cible: 98</x:v>
@@ -1454,7 +1454,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>KPI-006</x:v>
+        <x:v>KPI_006</x:v>
       </x:c>
       <x:c r="C50" t="str">
         <x:v>KPI-006 - VOLUME IVR | Calcul: Nombre total de transaction éligible pour le service | Cible: 98</x:v>
@@ -1465,7 +1465,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>KPI-007</x:v>
+        <x:v>KPI_007</x:v>
       </x:c>
       <x:c r="C51" t="str">
         <x:v>KPI-007 - TAUX DE FONCTIONNALITE DES SYSTEMES IVR | Calcul: Somme des temps d'indisponibilité X 100) / Temps total de disponibilité | Cible: 99</x:v>
@@ -1476,7 +1476,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>KPI-008</x:v>
+        <x:v>KPI_008</x:v>
       </x:c>
       <x:c r="C52" t="str">
         <x:v>KPI-008 - Nombre d'incident de sécurité | Calcul: Nombre total d'incidents identifié sur le système informatique | Cible: a definir</x:v>
@@ -1487,7 +1487,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>KPI-009</x:v>
+        <x:v>KPI_009</x:v>
       </x:c>
       <x:c r="C53" t="str">
         <x:v>KPI-009 - Taux de traitement dans les délais | Calcul: Nbre de ticket ouvert traités dans le délais(2880min)X100 / Nbre total d... | Cible: 89</x:v>
@@ -1498,7 +1498,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>KPI-010</x:v>
+        <x:v>KPI_010</x:v>
       </x:c>
       <x:c r="C54" t="str">
         <x:v>KPI-010 - MTTR | Calcul: Moyenne de temps de traitement de tous les tickets sur la periode | Cible: 60</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>KPI-011</x:v>
+        <x:v>KPI_011</x:v>
       </x:c>
       <x:c r="C55" t="str">
         <x:v>KPI-011 - Taux d'exactitude de réparation ou solution | Calcul: Volume total de tickets ouverts - Volume de tickets réouverts)X 100 / no... | Cible: 90</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>KPI-012</x:v>
+        <x:v>KPI_012</x:v>
       </x:c>
       <x:c r="C56" t="str">
         <x:v>KPI-012 - Tx Exact ECC | Calcul: Tx Exact ECC=Nb transactions sans ECC X 100/Nb transactions évaluées | Cible: 95</x:v>
@@ -1531,7 +1531,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>KPI-013</x:v>
+        <x:v>KPI_013</x:v>
       </x:c>
       <x:c r="C57" t="str">
         <x:v>KPI-013 - Tx Exact ECA | Calcul: Tx Exact ECA=Nb transactions sans ECA X 100/Nb transactions évaluées | Cible: 90</x:v>
@@ -1542,7 +1542,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>KPI-014</x:v>
+        <x:v>KPI_014</x:v>
       </x:c>
       <x:c r="C58" t="str">
         <x:v>KPI-014 - Tx Exact ECCo | Calcul: Tx Exact ECCo=Nb transactions sans ECCo X 100/Nb transactions évaluées | Cible: 99.5</x:v>
@@ -1553,7 +1553,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>KPI-015</x:v>
+        <x:v>KPI_015</x:v>
       </x:c>
       <x:c r="C59" t="str">
         <x:v>KPI-015 - Tx Exact ENC | Calcul: Tx Exact ENC=Nb transactions sans ENC X 100/Nb transactions évaluées | Cible: 95</x:v>
@@ -1564,7 +1564,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>KPI-016</x:v>
+        <x:v>KPI_016</x:v>
       </x:c>
       <x:c r="C60" t="str">
         <x:v>KPI-016 - Tx défaut | Calcul: Tx défaut=Nb d'inconformité X 100/Nb transactions évaluées | Cible: 2</x:v>
@@ -1575,7 +1575,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>KPI-017</x:v>
+        <x:v>KPI_017</x:v>
       </x:c>
       <x:c r="C61" t="str">
         <x:v>KPI-017 - Tx per de Esc | Calcul: Tx per de Esc= Pertinence de l’escalade = Nb d’escalades incorrectes / N... | Cible: 98</x:v>
@@ -1586,7 +1586,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>KPI-018</x:v>
+        <x:v>KPI_018</x:v>
       </x:c>
       <x:c r="C62" t="str">
         <x:v>KPI-018 - VR | Calcul: VR=Echantillonnage représentatif sur le volume d’appels reçu. Calcul eff... | Cible: 600</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>KPI-019</x:v>
+        <x:v>KPI_019</x:v>
       </x:c>
       <x:c r="C63" t="str">
         <x:v>KPI-019 - Taux de réussite Quiz FI | Calcul: Nombre d'apprenants ayant validé le quiz ÷ Nombre total d'apprenants aya... | Cible: 85</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>KPI-020</x:v>
+        <x:v>KPI_020</x:v>
       </x:c>
       <x:c r="C64" t="str">
         <x:v>KPI-020 - Heures FI (Prévues vs Réalisées) | Calcul: Heures FI réalisées /Heures FI prévues)​ * 100 | Cible: 100</x:v>
@@ -1619,7 +1619,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>KPI-021</x:v>
+        <x:v>KPI_021</x:v>
       </x:c>
       <x:c r="C65" t="str">
         <x:v>KPI-021 - Taux Présence Ateliers | Calcul: Nombre d'agents présents aux ateliers de formation ÷ Nombre d'agents con... | Cible: 95</x:v>
@@ -1630,7 +1630,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>KPI-022</x:v>
+        <x:v>KPI_022</x:v>
       </x:c>
       <x:c r="C66" t="str">
         <x:v>KPI-022 - Taux de Présence au Coaching | Calcul: Nombre de séances de coaching réalisées ÷ Nombre de séances de coaching ... | Cible: 95</x:v>
@@ -1641,7 +1641,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>KPI-023</x:v>
+        <x:v>KPI_023</x:v>
       </x:c>
       <x:c r="C67" t="str">
         <x:v>KPI-023 - Heures FC (Prévues vs Réalisées) | Calcul: Heures FC réalisées ÷ Heures FC prévues) × 100 | Cible: 95</x:v>
@@ -1652,7 +1652,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>KPI-024</x:v>
+        <x:v>KPI_024</x:v>
       </x:c>
       <x:c r="C68" t="str">
         <x:v>KPI-024 - Taux de Réussite Quiz FC | Calcul: Nombre d'agents ayant atteint ou dépassé le score minimum requis ÷ Nombr... | Cible: 95</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>KPI-025</x:v>
+        <x:v>KPI_025</x:v>
       </x:c>
       <x:c r="C69" t="str">
         <x:v>KPI-025 - Score Quiz FC | Calcul: Somme des scores individuels obtenus aux quiz FC ÷ Nombre total d'agents... | Cible: 95</x:v>
@@ -1674,7 +1674,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>KPI-026</x:v>
+        <x:v>KPI_026</x:v>
       </x:c>
       <x:c r="C70" t="str">
         <x:v>KPI-026 - Taux de complétion EDFLEX | Calcul: Nombre de parcours complétés ÷ Nombre de parcours assignés) × 100 | Cible: 100</x:v>
@@ -1685,7 +1685,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>KPI-027</x:v>
+        <x:v>KPI_027</x:v>
       </x:c>
       <x:c r="C71" t="str">
         <x:v>KPI-027 - Qualité de la Formation CRCD — Intégration | Calcul: Nombre d'agents ayant réussi au quiz ÷ Nombre total d'agents évalués) × 100 | Cible: 85</x:v>
@@ -1696,7 +1696,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>KPI-028</x:v>
+        <x:v>KPI_028</x:v>
       </x:c>
       <x:c r="C72" t="str">
         <x:v>KPI-028 - Qualité de la Formation CRCD — Continue | Calcul: Nombre d'agents ayant atteint le seuil ÷ Nombre total d'agents évalués) ... | Cible: 95</x:v>
@@ -1707,7 +1707,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>KPI-029</x:v>
+        <x:v>KPI_029</x:v>
       </x:c>
       <x:c r="C73" t="str">
         <x:v>KPI-029 - Efficacité de la Formation | Calcul: Une enquête de satisfaction sur le déroulé de la formation | Cible: 80</x:v>
@@ -1718,7 +1718,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>KPI-030</x:v>
+        <x:v>KPI_030</x:v>
       </x:c>
       <x:c r="C74" t="str">
         <x:v>KPI-030 - Efficacité du Formateur | Calcul: feedbacks à chaud ( enquête de satisfaction) | Cible: 80</x:v>
@@ -1729,7 +1729,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>KPI-031</x:v>
+        <x:v>KPI_031</x:v>
       </x:c>
       <x:c r="C75" t="str">
         <x:v>KPI-031 - Taux de Formation Réalisée | Calcul: Nombre de formation réalisée / Nombre de formation prévue) * 100 | Cible: 60</x:v>
@@ -1740,7 +1740,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>KPI-032</x:v>
+        <x:v>KPI_032</x:v>
       </x:c>
       <x:c r="C76" t="str">
         <x:v>KPI-032 - FOLLOWERS LINKEDIN | Calcul: NA | Cible: a definir</x:v>
@@ -1751,7 +1751,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>KPI-033</x:v>
+        <x:v>KPI_033</x:v>
       </x:c>
       <x:c r="C77" t="str">
         <x:v>KPI-033 - FOLLOWERS FACEBOOK | Calcul: NA | Cible: a definir</x:v>
@@ -1762,7 +1762,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>KPI-034</x:v>
+        <x:v>KPI_034</x:v>
       </x:c>
       <x:c r="C78" t="str">
         <x:v>KPI-034 - FOLLOWERS INSTAGRAM | Calcul: NA | Cible: a definir</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>KPI-035</x:v>
+        <x:v>KPI_035</x:v>
       </x:c>
       <x:c r="C79" t="str">
         <x:v>KPI-035 - FOLLOWERS SUR X (Twitter) | Calcul: NA | Cible: a definir</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>KPI-036</x:v>
+        <x:v>KPI_036</x:v>
       </x:c>
       <x:c r="C80" t="str">
         <x:v>KPI-036 - IMPRESSION (LINKEDIN) | Calcul: NA | Cible: a definir</x:v>
@@ -1795,7 +1795,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>KPI-037</x:v>
+        <x:v>KPI_037</x:v>
       </x:c>
       <x:c r="C81" t="str">
         <x:v>KPI-037 - PORTEE (FACEBOOK) | Calcul: NA | Cible: a definir</x:v>
@@ -1806,7 +1806,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>KPI-038</x:v>
+        <x:v>KPI_038</x:v>
       </x:c>
       <x:c r="C82" t="str">
         <x:v>KPI-038 - PORTEE (INSTAGRAM) | Calcul: NA | Cible: a definir</x:v>
@@ -1817,7 +1817,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>KPI-039</x:v>
+        <x:v>KPI_039</x:v>
       </x:c>
       <x:c r="C83" t="str">
         <x:v>KPI-039 - TAUX D'ENGAGEMENT | Calcul: INTERACTIONS/IMPRESSIONS) *100 | Cible: a definir</x:v>
@@ -1828,7 +1828,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>KPI-040</x:v>
+        <x:v>KPI_040</x:v>
       </x:c>
       <x:c r="C84" t="str">
         <x:v>KPI-040 - TAUX D'ENGAGEMENT FACEBOOK | Calcul: INTERACTIONS/PORTEE) * 100 | Cible: a definir</x:v>
@@ -1839,7 +1839,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>KPI-041</x:v>
+        <x:v>KPI_041</x:v>
       </x:c>
       <x:c r="C85" t="str">
         <x:v>KPI-041 - TAUX D'ENGAGEMENT INSTAGRAM | Calcul: INTERACTIONS/PORTEE) *100 | Cible: a definir</x:v>
@@ -1850,7 +1850,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>KPI-042</x:v>
+        <x:v>KPI_042</x:v>
       </x:c>
       <x:c r="C86" t="str">
         <x:v>KPI-042 - Masse Salariale | Calcul: Total des charges RH sur le total du Chiffre d'affaires | Cible: 35</x:v>
@@ -1861,7 +1861,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>KPI-043</x:v>
+        <x:v>KPI_043</x:v>
       </x:c>
       <x:c r="C87" t="str">
         <x:v>KPI-043 - Résultat Avant Impôt | Calcul: Chiffre d'affaires - toutes charges) / Chiffre d'affaires | Cible: 15</x:v>
@@ -1872,7 +1872,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>KPI-044</x:v>
+        <x:v>KPI_044</x:v>
       </x:c>
       <x:c r="C88" t="str">
         <x:v>KPI-044 - Taux de transformation digital | Calcul: Somme (%projet) / Nombre de projets | Cible: 70</x:v>
@@ -1883,7 +1883,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>KPI-045</x:v>
+        <x:v>KPI_045</x:v>
       </x:c>
       <x:c r="C89" t="str">
         <x:v>KPI-045 - Taux de recouvrement | Calcul: Somme des encaissements sur la période / Somme des créances exigibles su... | Cible: 75</x:v>
@@ -1894,7 +1894,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>KPI-046</x:v>
+        <x:v>KPI_046</x:v>
       </x:c>
       <x:c r="C90" t="str">
         <x:v>KPI-046 - Créances clients | Calcul: Somme des factures émises échues sur une période donnée | Cible: 1</x:v>
@@ -1905,7 +1905,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>KPI-047</x:v>
+        <x:v>KPI_047</x:v>
       </x:c>
       <x:c r="C91" t="str">
         <x:v>KPI-047 - Encours Clients | Calcul: Somme des créances clients (Factures échues et non échues) + Commandes e... | Cible: 1</x:v>
@@ -1916,7 +1916,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>KPI-048</x:v>
+        <x:v>KPI_048</x:v>
       </x:c>
       <x:c r="C92" t="str">
         <x:v>KPI-048 - Balance Âgée | Calcul: Date du jour - date d'échéance de la facture | Cible: 25</x:v>
@@ -1927,7 +1927,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>KPI-049</x:v>
+        <x:v>KPI_049</x:v>
       </x:c>
       <x:c r="C93" t="str">
         <x:v>KPI-049 - DSO (Days Sales Outstanding) | Calcul: Créances clients / Chiffre d’affaires TTC sur la période) × Nombre de jo... | Cible: 45</x:v>
@@ -1938,7 +1938,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>KPI-050</x:v>
+        <x:v>KPI_050</x:v>
       </x:c>
       <x:c r="C94" t="str">
         <x:v>KPI-050 - Point des Encaissements | Calcul: Somme réelle des encaissements sur une période donnée (virements, chèque... | Cible: 1</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>KPI-051</x:v>
+        <x:v>KPI_051</x:v>
       </x:c>
       <x:c r="C95" t="str">
         <x:v>KPI-051 - Créances Irrécouvrables | Calcul: Créances douteuses / CA total). | Cible: 5</x:v>
@@ -1960,7 +1960,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>KPI-052</x:v>
+        <x:v>KPI_052</x:v>
       </x:c>
       <x:c r="C96" t="str">
         <x:v>KPI-052 - ADHERENCE HEURE | Calcul: Heures réalisées (temps total de présence - temps de déjeuner) /heures p... | Cible: 90</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>KPI-053</x:v>
+        <x:v>KPI_053</x:v>
       </x:c>
       <x:c r="C97" t="str">
         <x:v>KPI-053 - TAUX D'OCCUPATION | Calcul: Traitement + attente ) /( Traitement + attente + post appel ) )* 100 | Cible: 75</x:v>
@@ -1982,7 +1982,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>KPI-054</x:v>
+        <x:v>KPI_054</x:v>
       </x:c>
       <x:c r="C98" t="str">
         <x:v>KPI-054 - ADHERENCE PLANNING | Calcul: ETP (EFFECTIF TOTAL PLANIFIES) / BESOIN ) )* 100 | Cible: 90</x:v>
@@ -1993,7 +1993,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>KPI-055</x:v>
+        <x:v>KPI_055</x:v>
       </x:c>
       <x:c r="C99" t="str">
         <x:v>KPI-055 - QUALITE DE PREVISION | Calcul: RECUS / PREVUS | Cible: 90</x:v>
@@ -2004,7 +2004,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>KPI-056</x:v>
+        <x:v>KPI_056</x:v>
       </x:c>
       <x:c r="C100" t="str">
         <x:v>KPI-056 - EFFICACITE | Calcul: TRAITES/RECUS | Cible: 95</x:v>
@@ -2015,7 +2015,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B101" t="str">
-        <x:v>KPI-057</x:v>
+        <x:v>KPI_057</x:v>
       </x:c>
       <x:c r="C101" t="str">
         <x:v>KPI-057 - Volume total des achats | Calcul: Somme des montants des bons de commande et bons d'achat émis sur la période | Cible: a definir</x:v>
@@ -2026,7 +2026,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B102" t="str">
-        <x:v>KPI-058</x:v>
+        <x:v>KPI_058</x:v>
       </x:c>
       <x:c r="C102" t="str">
         <x:v>KPI-058 - Taux de conformité des bons de commande | Calcul: Nombre de bons de commande conformes / Nombre total de bons de commande)... | Cible: 95</x:v>
@@ -2037,7 +2037,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B103" t="str">
-        <x:v>KPI-059</x:v>
+        <x:v>KPI_059</x:v>
       </x:c>
       <x:c r="C103" t="str">
         <x:v>KPI-059 - Taux de non-conformité des produits | Calcul: Nombre de produits retournés ou non conformes / Total des produits achet... | Cible: 1</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B104" t="str">
-        <x:v>KPI-060</x:v>
+        <x:v>KPI_060</x:v>
       </x:c>
       <x:c r="C104" t="str">
         <x:v>KPI-060 - Délai moyen d'approvisionnement | Calcul: Somme des délais individuels d'approvisionnement / Nombre de demandes tr... | Cible: a definir</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B105" t="str">
-        <x:v>KPI-061</x:v>
+        <x:v>KPI_061</x:v>
       </x:c>
       <x:c r="C105" t="str">
         <x:v>KPI-061 - Taux de service client | Calcul: Nombre de demandes satisfaites / Nombre total de demandes exprimées) × 100 | Cible: 90</x:v>
@@ -2070,7 +2070,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B106" t="str">
-        <x:v>KPI-062</x:v>
+        <x:v>KPI_062</x:v>
       </x:c>
       <x:c r="C106" t="str">
         <x:v>KPI-062 - Taux de disponibilité du stock critique | Calcul: Nombre d'articles critiques disponibles / Nombre total d'articles critiq... | Cible: 90</x:v>
@@ -2081,7 +2081,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B107" t="str">
-        <x:v>KPI-063</x:v>
+        <x:v>KPI_063</x:v>
       </x:c>
       <x:c r="C107" t="str">
         <x:v>KPI-063 - OOS | Calcul: TRO OOS (%) = Objectif (%) /Réalisé(%) | Cible: 19.7</x:v>
@@ -2092,7 +2092,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B108" t="str">
-        <x:v>KPI-064</x:v>
+        <x:v>KPI_064</x:v>
       </x:c>
       <x:c r="C108" t="str">
         <x:v>KPI-064 - DTR (Direct To Retail) | Calcul: TRO DTR (%) = (Réalisé DTR / Objectif DTR) × 100 | Cible: 100</x:v>
@@ -2103,7 +2103,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B109" t="str">
-        <x:v>KPI-065</x:v>
+        <x:v>KPI_065</x:v>
       </x:c>
       <x:c r="C109" t="str">
         <x:v>KPI-065 - DTC (Direct To Consumer) | Calcul: TRO DTC (%) = (Réalisé DTC / Objectif DTC) × 100 | Cible: 100</x:v>
@@ -2114,7 +2114,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B110" t="str">
-        <x:v>KPI-066</x:v>
+        <x:v>KPI_066</x:v>
       </x:c>
       <x:c r="C110" t="str">
         <x:v>KPI-066 - ADU (Active Data Users) | Calcul: TRO ADU (%) = (ADU Réalisé / ADU Objectif) × 100 | Cible: 100</x:v>
@@ -2125,7 +2125,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B111" t="str">
-        <x:v>KPI-067</x:v>
+        <x:v>KPI_067</x:v>
       </x:c>
       <x:c r="C111" t="str">
         <x:v>KPI-067 - MAU (MoMo Active Users) | Calcul: TRO MAU (%) = (MAU Réalisé / MAU Objectif) × 100 | Cible: 100</x:v>
@@ -2136,7 +2136,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B112" t="str">
-        <x:v>KPI-068</x:v>
+        <x:v>KPI_068</x:v>
       </x:c>
       <x:c r="C112" t="str">
         <x:v>KPI-068 - FTTH (Fiber To The Home) | Calcul: TRO FTTH (%) = (FTTH Réalisé / FTTH Objectif) × 100 | Cible: 100</x:v>
@@ -2147,7 +2147,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B113" t="str">
-        <x:v>KPI-069</x:v>
+        <x:v>KPI_069</x:v>
       </x:c>
       <x:c r="C113" t="str">
         <x:v>KPI-069 - FWA (Fixed Wireless Access) | Calcul: TRO FWA (%) = (FWA Réalisé / FWA Objectif) × 100 | Cible: 100</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B114" t="str">
-        <x:v>KPI-070</x:v>
+        <x:v>KPI_070</x:v>
       </x:c>
       <x:c r="C114" t="str">
         <x:v>KPI-070 - Services at Touch Point (SATP) | Calcul: SATP(%) = (NPS AGENT + NPS AGENCE)/2 | Cible: 100</x:v>
@@ -2169,7 +2169,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B115" t="str">
-        <x:v>KPI-071</x:v>
+        <x:v>KPI_071</x:v>
       </x:c>
       <x:c r="C115" t="str">
         <x:v>KPI-071 - Recrutement Commerciaux (MRE) | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
@@ -2180,7 +2180,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B116" t="str">
-        <x:v>KPI-072</x:v>
+        <x:v>KPI_072</x:v>
       </x:c>
       <x:c r="C116" t="str">
         <x:v>KPI-072 - Performance MRE | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B117" t="str">
-        <x:v>KPI-073</x:v>
+        <x:v>KPI_073</x:v>
       </x:c>
       <x:c r="C117" t="str">
         <x:v>KPI-073 - Recrutement TDR | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B118" t="str">
-        <x:v>KPI-074</x:v>
+        <x:v>KPI_074</x:v>
       </x:c>
       <x:c r="C118" t="str">
         <x:v>KPI-074 - Performance TDR | Calcul: TRO = (Réalisé / Objectif) × 100 | Cible: 100</x:v>
@@ -2213,7 +2213,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B119" t="str">
-        <x:v>KPI-075</x:v>
+        <x:v>KPI_075</x:v>
       </x:c>
       <x:c r="C119" t="str">
         <x:v>KPI-075 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B120" t="str">
-        <x:v>KPI-076</x:v>
+        <x:v>KPI_076</x:v>
       </x:c>
       <x:c r="C120" t="str">
         <x:v>KPI-076 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2235,7 +2235,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B121" t="str">
-        <x:v>KPI-077</x:v>
+        <x:v>KPI_077</x:v>
       </x:c>
       <x:c r="C121" t="str">
         <x:v>KPI-077 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2246,7 +2246,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B122" t="str">
-        <x:v>KPI-078</x:v>
+        <x:v>KPI_078</x:v>
       </x:c>
       <x:c r="C122" t="str">
         <x:v>KPI-078 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2257,7 +2257,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B123" t="str">
-        <x:v>KPI-079</x:v>
+        <x:v>KPI_079</x:v>
       </x:c>
       <x:c r="C123" t="str">
         <x:v>KPI-079 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2268,7 +2268,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B124" t="str">
-        <x:v>KPI-080</x:v>
+        <x:v>KPI_080</x:v>
       </x:c>
       <x:c r="C124" t="str">
         <x:v>KPI-080 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2279,7 +2279,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B125" t="str">
-        <x:v>KPI-081</x:v>
+        <x:v>KPI_081</x:v>
       </x:c>
       <x:c r="C125" t="str">
         <x:v>KPI-081 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2290,7 +2290,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B126" t="str">
-        <x:v>KPI-082</x:v>
+        <x:v>KPI_082</x:v>
       </x:c>
       <x:c r="C126" t="str">
         <x:v>KPI-082 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2301,7 +2301,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B127" t="str">
-        <x:v>KPI-083</x:v>
+        <x:v>KPI_083</x:v>
       </x:c>
       <x:c r="C127" t="str">
         <x:v>KPI-083 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2312,7 +2312,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B128" t="str">
-        <x:v>KPI-084</x:v>
+        <x:v>KPI_084</x:v>
       </x:c>
       <x:c r="C128" t="str">
         <x:v>KPI-084 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2323,7 +2323,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B129" t="str">
-        <x:v>KPI-085</x:v>
+        <x:v>KPI_085</x:v>
       </x:c>
       <x:c r="C129" t="str">
         <x:v>KPI-085 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2334,7 +2334,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B130" t="str">
-        <x:v>KPI-086</x:v>
+        <x:v>KPI_086</x:v>
       </x:c>
       <x:c r="C130" t="str">
         <x:v>KPI-086 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2345,7 +2345,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B131" t="str">
-        <x:v>KPI-087</x:v>
+        <x:v>KPI_087</x:v>
       </x:c>
       <x:c r="C131" t="str">
         <x:v>KPI-087 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2356,7 +2356,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B132" t="str">
-        <x:v>KPI-088</x:v>
+        <x:v>KPI_088</x:v>
       </x:c>
       <x:c r="C132" t="str">
         <x:v>KPI-088 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2367,7 +2367,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B133" t="str">
-        <x:v>KPI-089</x:v>
+        <x:v>KPI_089</x:v>
       </x:c>
       <x:c r="C133" t="str">
         <x:v>KPI-089 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2378,7 +2378,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B134" t="str">
-        <x:v>KPI-090</x:v>
+        <x:v>KPI_090</x:v>
       </x:c>
       <x:c r="C134" t="str">
         <x:v>KPI-090 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2389,7 +2389,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B135" t="str">
-        <x:v>KPI-091</x:v>
+        <x:v>KPI_091</x:v>
       </x:c>
       <x:c r="C135" t="str">
         <x:v>KPI-091 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2400,7 +2400,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B136" t="str">
-        <x:v>KPI-092</x:v>
+        <x:v>KPI_092</x:v>
       </x:c>
       <x:c r="C136" t="str">
         <x:v>KPI-092 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2411,7 +2411,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B137" t="str">
-        <x:v>KPI-093</x:v>
+        <x:v>KPI_093</x:v>
       </x:c>
       <x:c r="C137" t="str">
         <x:v>KPI-093 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2422,7 +2422,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B138" t="str">
-        <x:v>KPI-094</x:v>
+        <x:v>KPI_094</x:v>
       </x:c>
       <x:c r="C138" t="str">
         <x:v>KPI-094 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B139" t="str">
-        <x:v>KPI-095</x:v>
+        <x:v>KPI_095</x:v>
       </x:c>
       <x:c r="C139" t="str">
         <x:v>KPI-095 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2444,7 +2444,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B140" t="str">
-        <x:v>KPI-096</x:v>
+        <x:v>KPI_096</x:v>
       </x:c>
       <x:c r="C140" t="str">
         <x:v>KPI-096 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2455,7 +2455,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B141" t="str">
-        <x:v>KPI-097</x:v>
+        <x:v>KPI_097</x:v>
       </x:c>
       <x:c r="C141" t="str">
         <x:v>KPI-097 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2466,7 +2466,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B142" t="str">
-        <x:v>KPI-098</x:v>
+        <x:v>KPI_098</x:v>
       </x:c>
       <x:c r="C142" t="str">
         <x:v>KPI-098 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2477,7 +2477,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B143" t="str">
-        <x:v>KPI-099</x:v>
+        <x:v>KPI_099</x:v>
       </x:c>
       <x:c r="C143" t="str">
         <x:v>KPI-099 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2488,7 +2488,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B144" t="str">
-        <x:v>KPI-100</x:v>
+        <x:v>KPI_100</x:v>
       </x:c>
       <x:c r="C144" t="str">
         <x:v>KPI-100 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2499,7 +2499,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B145" t="str">
-        <x:v>KPI-101</x:v>
+        <x:v>KPI_101</x:v>
       </x:c>
       <x:c r="C145" t="str">
         <x:v>KPI-101 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2510,7 +2510,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B146" t="str">
-        <x:v>KPI-102</x:v>
+        <x:v>KPI_102</x:v>
       </x:c>
       <x:c r="C146" t="str">
         <x:v>KPI-102 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B147" t="str">
-        <x:v>KPI-103</x:v>
+        <x:v>KPI_103</x:v>
       </x:c>
       <x:c r="C147" t="str">
         <x:v>KPI-103 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2532,7 +2532,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B148" t="str">
-        <x:v>KPI-104</x:v>
+        <x:v>KPI_104</x:v>
       </x:c>
       <x:c r="C148" t="str">
         <x:v>KPI-104 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B149" t="str">
-        <x:v>KPI-105</x:v>
+        <x:v>KPI_105</x:v>
       </x:c>
       <x:c r="C149" t="str">
         <x:v>KPI-105 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2554,7 +2554,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B150" t="str">
-        <x:v>KPI-106</x:v>
+        <x:v>KPI_106</x:v>
       </x:c>
       <x:c r="C150" t="str">
         <x:v>KPI-106 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2565,7 +2565,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B151" t="str">
-        <x:v>KPI-107</x:v>
+        <x:v>KPI_107</x:v>
       </x:c>
       <x:c r="C151" t="str">
         <x:v>KPI-107 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B152" t="str">
-        <x:v>KPI-108</x:v>
+        <x:v>KPI_108</x:v>
       </x:c>
       <x:c r="C152" t="str">
         <x:v>KPI-108 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2587,7 +2587,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>KPI-109</x:v>
+        <x:v>KPI_109</x:v>
       </x:c>
       <x:c r="C153" t="str">
         <x:v>KPI-109 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2598,7 +2598,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B154" t="str">
-        <x:v>KPI-110</x:v>
+        <x:v>KPI_110</x:v>
       </x:c>
       <x:c r="C154" t="str">
         <x:v>KPI-110 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B155" t="str">
-        <x:v>KPI-111</x:v>
+        <x:v>KPI_111</x:v>
       </x:c>
       <x:c r="C155" t="str">
         <x:v>KPI-111 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2620,7 +2620,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B156" t="str">
-        <x:v>KPI-112</x:v>
+        <x:v>KPI_112</x:v>
       </x:c>
       <x:c r="C156" t="str">
         <x:v>KPI-112 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2631,7 +2631,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B157" t="str">
-        <x:v>KPI-113</x:v>
+        <x:v>KPI_113</x:v>
       </x:c>
       <x:c r="C157" t="str">
         <x:v>KPI-113 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2642,7 +2642,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B158" t="str">
-        <x:v>KPI-114</x:v>
+        <x:v>KPI_114</x:v>
       </x:c>
       <x:c r="C158" t="str">
         <x:v>KPI-114 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2653,7 +2653,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B159" t="str">
-        <x:v>KPI-115</x:v>
+        <x:v>KPI_115</x:v>
       </x:c>
       <x:c r="C159" t="str">
         <x:v>KPI-115 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2664,7 +2664,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B160" t="str">
-        <x:v>KPI-116</x:v>
+        <x:v>KPI_116</x:v>
       </x:c>
       <x:c r="C160" t="str">
         <x:v>KPI-116 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2675,7 +2675,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B161" t="str">
-        <x:v>KPI-117</x:v>
+        <x:v>KPI_117</x:v>
       </x:c>
       <x:c r="C161" t="str">
         <x:v>KPI-117 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2686,7 +2686,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B162" t="str">
-        <x:v>KPI-118</x:v>
+        <x:v>KPI_118</x:v>
       </x:c>
       <x:c r="C162" t="str">
         <x:v>KPI-118 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2697,7 +2697,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B163" t="str">
-        <x:v>KPI-119</x:v>
+        <x:v>KPI_119</x:v>
       </x:c>
       <x:c r="C163" t="str">
         <x:v>KPI-119 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2708,7 +2708,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B164" t="str">
-        <x:v>KPI-120</x:v>
+        <x:v>KPI_120</x:v>
       </x:c>
       <x:c r="C164" t="str">
         <x:v>KPI-120 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2719,7 +2719,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B165" t="str">
-        <x:v>KPI-121</x:v>
+        <x:v>KPI_121</x:v>
       </x:c>
       <x:c r="C165" t="str">
         <x:v>KPI-121 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2730,7 +2730,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B166" t="str">
-        <x:v>KPI-122</x:v>
+        <x:v>KPI_122</x:v>
       </x:c>
       <x:c r="C166" t="str">
         <x:v>KPI-122 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2741,7 +2741,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B167" t="str">
-        <x:v>KPI-123</x:v>
+        <x:v>KPI_123</x:v>
       </x:c>
       <x:c r="C167" t="str">
         <x:v>KPI-123 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2752,7 +2752,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B168" t="str">
-        <x:v>KPI-124</x:v>
+        <x:v>KPI_124</x:v>
       </x:c>
       <x:c r="C168" t="str">
         <x:v>KPI-124 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2763,7 +2763,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B169" t="str">
-        <x:v>KPI-125</x:v>
+        <x:v>KPI_125</x:v>
       </x:c>
       <x:c r="C169" t="str">
         <x:v>KPI-125 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2774,7 +2774,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B170" t="str">
-        <x:v>KPI-126</x:v>
+        <x:v>KPI_126</x:v>
       </x:c>
       <x:c r="C170" t="str">
         <x:v>KPI-126 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2785,7 +2785,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B171" t="str">
-        <x:v>KPI-127</x:v>
+        <x:v>KPI_127</x:v>
       </x:c>
       <x:c r="C171" t="str">
         <x:v>KPI-127 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2796,7 +2796,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B172" t="str">
-        <x:v>KPI-128</x:v>
+        <x:v>KPI_128</x:v>
       </x:c>
       <x:c r="C172" t="str">
         <x:v>KPI-128 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2807,7 +2807,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B173" t="str">
-        <x:v>KPI-129</x:v>
+        <x:v>KPI_129</x:v>
       </x:c>
       <x:c r="C173" t="str">
         <x:v>KPI-129 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2818,7 +2818,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B174" t="str">
-        <x:v>KPI-130</x:v>
+        <x:v>KPI_130</x:v>
       </x:c>
       <x:c r="C174" t="str">
         <x:v>KPI-130 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2829,7 +2829,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B175" t="str">
-        <x:v>KPI-131</x:v>
+        <x:v>KPI_131</x:v>
       </x:c>
       <x:c r="C175" t="str">
         <x:v>KPI-131 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2840,7 +2840,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B176" t="str">
-        <x:v>KPI-132</x:v>
+        <x:v>KPI_132</x:v>
       </x:c>
       <x:c r="C176" t="str">
         <x:v>KPI-132 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2851,7 +2851,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B177" t="str">
-        <x:v>KPI-133</x:v>
+        <x:v>KPI_133</x:v>
       </x:c>
       <x:c r="C177" t="str">
         <x:v>KPI-133 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2862,7 +2862,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B178" t="str">
-        <x:v>KPI-134</x:v>
+        <x:v>KPI_134</x:v>
       </x:c>
       <x:c r="C178" t="str">
         <x:v>KPI-134 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2873,7 +2873,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B179" t="str">
-        <x:v>KPI-135</x:v>
+        <x:v>KPI_135</x:v>
       </x:c>
       <x:c r="C179" t="str">
         <x:v>KPI-135 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2884,7 +2884,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B180" t="str">
-        <x:v>KPI-136</x:v>
+        <x:v>KPI_136</x:v>
       </x:c>
       <x:c r="C180" t="str">
         <x:v>KPI-136 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B181" t="str">
-        <x:v>KPI-137</x:v>
+        <x:v>KPI_137</x:v>
       </x:c>
       <x:c r="C181" t="str">
         <x:v>KPI-137 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2906,7 +2906,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B182" t="str">
-        <x:v>KPI-138</x:v>
+        <x:v>KPI_138</x:v>
       </x:c>
       <x:c r="C182" t="str">
         <x:v>KPI-138 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2917,7 +2917,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B183" t="str">
-        <x:v>KPI-139</x:v>
+        <x:v>KPI_139</x:v>
       </x:c>
       <x:c r="C183" t="str">
         <x:v>KPI-139 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2928,7 +2928,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B184" t="str">
-        <x:v>KPI-140</x:v>
+        <x:v>KPI_140</x:v>
       </x:c>
       <x:c r="C184" t="str">
         <x:v>KPI-140 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2939,7 +2939,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B185" t="str">
-        <x:v>KPI-141</x:v>
+        <x:v>KPI_141</x:v>
       </x:c>
       <x:c r="C185" t="str">
         <x:v>KPI-141 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2950,7 +2950,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B186" t="str">
-        <x:v>KPI-142</x:v>
+        <x:v>KPI_142</x:v>
       </x:c>
       <x:c r="C186" t="str">
         <x:v>KPI-142 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2961,7 +2961,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B187" t="str">
-        <x:v>KPI-143</x:v>
+        <x:v>KPI_143</x:v>
       </x:c>
       <x:c r="C187" t="str">
         <x:v>KPI-143 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2972,7 +2972,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B188" t="str">
-        <x:v>KPI-144</x:v>
+        <x:v>KPI_144</x:v>
       </x:c>
       <x:c r="C188" t="str">
         <x:v>KPI-144 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B189" t="str">
-        <x:v>KPI-145</x:v>
+        <x:v>KPI_145</x:v>
       </x:c>
       <x:c r="C189" t="str">
         <x:v>KPI-145 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -2994,7 +2994,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B190" t="str">
-        <x:v>KPI-146</x:v>
+        <x:v>KPI_146</x:v>
       </x:c>
       <x:c r="C190" t="str">
         <x:v>KPI-146 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3005,7 +3005,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B191" t="str">
-        <x:v>KPI-147</x:v>
+        <x:v>KPI_147</x:v>
       </x:c>
       <x:c r="C191" t="str">
         <x:v>KPI-147 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3016,7 +3016,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B192" t="str">
-        <x:v>KPI-148</x:v>
+        <x:v>KPI_148</x:v>
       </x:c>
       <x:c r="C192" t="str">
         <x:v>KPI-148 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B193" t="str">
-        <x:v>KPI-149</x:v>
+        <x:v>KPI_149</x:v>
       </x:c>
       <x:c r="C193" t="str">
         <x:v>KPI-149 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3038,7 +3038,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B194" t="str">
-        <x:v>KPI-150</x:v>
+        <x:v>KPI_150</x:v>
       </x:c>
       <x:c r="C194" t="str">
         <x:v>KPI-150 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3049,7 +3049,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B195" t="str">
-        <x:v>KPI-151</x:v>
+        <x:v>KPI_151</x:v>
       </x:c>
       <x:c r="C195" t="str">
         <x:v>KPI-151 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3060,7 +3060,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B196" t="str">
-        <x:v>KPI-152</x:v>
+        <x:v>KPI_152</x:v>
       </x:c>
       <x:c r="C196" t="str">
         <x:v>KPI-152 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3071,7 +3071,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B197" t="str">
-        <x:v>KPI-153</x:v>
+        <x:v>KPI_153</x:v>
       </x:c>
       <x:c r="C197" t="str">
         <x:v>KPI-153 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3082,7 +3082,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B198" t="str">
-        <x:v>KPI-154</x:v>
+        <x:v>KPI_154</x:v>
       </x:c>
       <x:c r="C198" t="str">
         <x:v>KPI-154 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3093,7 +3093,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B199" t="str">
-        <x:v>KPI-155</x:v>
+        <x:v>KPI_155</x:v>
       </x:c>
       <x:c r="C199" t="str">
         <x:v>KPI-155 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B200" t="str">
-        <x:v>KPI-156</x:v>
+        <x:v>KPI_156</x:v>
       </x:c>
       <x:c r="C200" t="str">
         <x:v>KPI-156 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3115,7 +3115,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B201" t="str">
-        <x:v>KPI-157</x:v>
+        <x:v>KPI_157</x:v>
       </x:c>
       <x:c r="C201" t="str">
         <x:v>KPI-157 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3126,7 +3126,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B202" t="str">
-        <x:v>KPI-158</x:v>
+        <x:v>KPI_158</x:v>
       </x:c>
       <x:c r="C202" t="str">
         <x:v>KPI-158 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3137,7 +3137,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B203" t="str">
-        <x:v>KPI-159</x:v>
+        <x:v>KPI_159</x:v>
       </x:c>
       <x:c r="C203" t="str">
         <x:v>KPI-159 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3148,7 +3148,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B204" t="str">
-        <x:v>KPI-160</x:v>
+        <x:v>KPI_160</x:v>
       </x:c>
       <x:c r="C204" t="str">
         <x:v>KPI-160 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3159,7 +3159,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B205" t="str">
-        <x:v>KPI-161</x:v>
+        <x:v>KPI_161</x:v>
       </x:c>
       <x:c r="C205" t="str">
         <x:v>KPI-161 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3170,7 +3170,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B206" t="str">
-        <x:v>KPI-162</x:v>
+        <x:v>KPI_162</x:v>
       </x:c>
       <x:c r="C206" t="str">
         <x:v>KPI-162 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3181,7 +3181,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B207" t="str">
-        <x:v>KPI-163</x:v>
+        <x:v>KPI_163</x:v>
       </x:c>
       <x:c r="C207" t="str">
         <x:v>KPI-163 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3192,7 +3192,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B208" t="str">
-        <x:v>KPI-164</x:v>
+        <x:v>KPI_164</x:v>
       </x:c>
       <x:c r="C208" t="str">
         <x:v>KPI-164 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3203,7 +3203,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B209" t="str">
-        <x:v>KPI-165</x:v>
+        <x:v>KPI_165</x:v>
       </x:c>
       <x:c r="C209" t="str">
         <x:v>KPI-165 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3214,7 +3214,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B210" t="str">
-        <x:v>KPI-166</x:v>
+        <x:v>KPI_166</x:v>
       </x:c>
       <x:c r="C210" t="str">
         <x:v>KPI-166 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3225,7 +3225,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B211" t="str">
-        <x:v>KPI-167</x:v>
+        <x:v>KPI_167</x:v>
       </x:c>
       <x:c r="C211" t="str">
         <x:v>KPI-167 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3236,7 +3236,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B212" t="str">
-        <x:v>KPI-168</x:v>
+        <x:v>KPI_168</x:v>
       </x:c>
       <x:c r="C212" t="str">
         <x:v>KPI-168 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3247,7 +3247,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B213" t="str">
-        <x:v>KPI-169</x:v>
+        <x:v>KPI_169</x:v>
       </x:c>
       <x:c r="C213" t="str">
         <x:v>KPI-169 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3258,7 +3258,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B214" t="str">
-        <x:v>KPI-170</x:v>
+        <x:v>KPI_170</x:v>
       </x:c>
       <x:c r="C214" t="str">
         <x:v>KPI-170 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3269,7 +3269,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B215" t="str">
-        <x:v>KPI-171</x:v>
+        <x:v>KPI_171</x:v>
       </x:c>
       <x:c r="C215" t="str">
         <x:v>KPI-171 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3280,7 +3280,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B216" t="str">
-        <x:v>KPI-172</x:v>
+        <x:v>KPI_172</x:v>
       </x:c>
       <x:c r="C216" t="str">
         <x:v>KPI-172 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3291,7 +3291,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B217" t="str">
-        <x:v>KPI-173</x:v>
+        <x:v>KPI_173</x:v>
       </x:c>
       <x:c r="C217" t="str">
         <x:v>KPI-173 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3302,7 +3302,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B218" t="str">
-        <x:v>KPI-174</x:v>
+        <x:v>KPI_174</x:v>
       </x:c>
       <x:c r="C218" t="str">
         <x:v>KPI-174 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3313,7 +3313,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B219" t="str">
-        <x:v>KPI-175</x:v>
+        <x:v>KPI_175</x:v>
       </x:c>
       <x:c r="C219" t="str">
         <x:v>KPI-175 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3324,7 +3324,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B220" t="str">
-        <x:v>KPI-176</x:v>
+        <x:v>KPI_176</x:v>
       </x:c>
       <x:c r="C220" t="str">
         <x:v>KPI-176 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3335,7 +3335,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B221" t="str">
-        <x:v>KPI-177</x:v>
+        <x:v>KPI_177</x:v>
       </x:c>
       <x:c r="C221" t="str">
         <x:v>KPI-177 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3346,7 +3346,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B222" t="str">
-        <x:v>KPI-178</x:v>
+        <x:v>KPI_178</x:v>
       </x:c>
       <x:c r="C222" t="str">
         <x:v>KPI-178 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3357,7 +3357,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B223" t="str">
-        <x:v>KPI-179</x:v>
+        <x:v>KPI_179</x:v>
       </x:c>
       <x:c r="C223" t="str">
         <x:v>KPI-179 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3368,7 +3368,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B224" t="str">
-        <x:v>KPI-180</x:v>
+        <x:v>KPI_180</x:v>
       </x:c>
       <x:c r="C224" t="str">
         <x:v>KPI-180 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3379,7 +3379,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B225" t="str">
-        <x:v>KPI-181</x:v>
+        <x:v>KPI_181</x:v>
       </x:c>
       <x:c r="C225" t="str">
         <x:v>KPI-181 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3390,7 +3390,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B226" t="str">
-        <x:v>KPI-182</x:v>
+        <x:v>KPI_182</x:v>
       </x:c>
       <x:c r="C226" t="str">
         <x:v>KPI-182 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3401,7 +3401,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B227" t="str">
-        <x:v>KPI-183</x:v>
+        <x:v>KPI_183</x:v>
       </x:c>
       <x:c r="C227" t="str">
         <x:v>KPI-183 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3412,7 +3412,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B228" t="str">
-        <x:v>KPI-184</x:v>
+        <x:v>KPI_184</x:v>
       </x:c>
       <x:c r="C228" t="str">
         <x:v>KPI-184 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3423,7 +3423,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B229" t="str">
-        <x:v>KPI-185</x:v>
+        <x:v>KPI_185</x:v>
       </x:c>
       <x:c r="C229" t="str">
         <x:v>KPI-185 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3434,7 +3434,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B230" t="str">
-        <x:v>KPI-186</x:v>
+        <x:v>KPI_186</x:v>
       </x:c>
       <x:c r="C230" t="str">
         <x:v>KPI-186 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3445,7 +3445,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B231" t="str">
-        <x:v>KPI-187</x:v>
+        <x:v>KPI_187</x:v>
       </x:c>
       <x:c r="C231" t="str">
         <x:v>KPI-187 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3456,7 +3456,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B232" t="str">
-        <x:v>KPI-188</x:v>
+        <x:v>KPI_188</x:v>
       </x:c>
       <x:c r="C232" t="str">
         <x:v>KPI-188 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3467,7 +3467,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B233" t="str">
-        <x:v>KPI-189</x:v>
+        <x:v>KPI_189</x:v>
       </x:c>
       <x:c r="C233" t="str">
         <x:v>KPI-189 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3478,7 +3478,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B234" t="str">
-        <x:v>KPI-190</x:v>
+        <x:v>KPI_190</x:v>
       </x:c>
       <x:c r="C234" t="str">
         <x:v>KPI-190 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3489,7 +3489,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B235" t="str">
-        <x:v>KPI-191</x:v>
+        <x:v>KPI_191</x:v>
       </x:c>
       <x:c r="C235" t="str">
         <x:v>KPI-191 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3500,7 +3500,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B236" t="str">
-        <x:v>KPI-192</x:v>
+        <x:v>KPI_192</x:v>
       </x:c>
       <x:c r="C236" t="str">
         <x:v>KPI-192 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3511,7 +3511,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B237" t="str">
-        <x:v>KPI-193</x:v>
+        <x:v>KPI_193</x:v>
       </x:c>
       <x:c r="C237" t="str">
         <x:v>KPI-193 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3522,7 +3522,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B238" t="str">
-        <x:v>KPI-194</x:v>
+        <x:v>KPI_194</x:v>
       </x:c>
       <x:c r="C238" t="str">
         <x:v>KPI-194 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B239" t="str">
-        <x:v>KPI-195</x:v>
+        <x:v>KPI_195</x:v>
       </x:c>
       <x:c r="C239" t="str">
         <x:v>KPI-195 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3544,7 +3544,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B240" t="str">
-        <x:v>KPI-196</x:v>
+        <x:v>KPI_196</x:v>
       </x:c>
       <x:c r="C240" t="str">
         <x:v>KPI-196 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3555,7 +3555,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B241" t="str">
-        <x:v>KPI-197</x:v>
+        <x:v>KPI_197</x:v>
       </x:c>
       <x:c r="C241" t="str">
         <x:v>KPI-197 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3566,7 +3566,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B242" t="str">
-        <x:v>KPI-198</x:v>
+        <x:v>KPI_198</x:v>
       </x:c>
       <x:c r="C242" t="str">
         <x:v>KPI-198 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3577,7 +3577,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B243" t="str">
-        <x:v>KPI-199</x:v>
+        <x:v>KPI_199</x:v>
       </x:c>
       <x:c r="C243" t="str">
         <x:v>KPI-199 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
@@ -3588,7 +3588,7 @@
         <x:v>kpi_ids</x:v>
       </x:c>
       <x:c r="B244" t="str">
-        <x:v>KPI-200</x:v>
+        <x:v>KPI_200</x:v>
       </x:c>
       <x:c r="C244" t="str">
         <x:v>KPI-200 - Reserve nouveau KPI | A declarer dans le Formulaire 1</x:v>
